--- a/data/data_monitoreo_huanchaquito.xlsx
+++ b/data/data_monitoreo_huanchaquito.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3">
@@ -457,117 +457,117 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SANCHEZ CORTEZ LEYLA DIANA</t>
+          <t>RODRIGUEZ RUBIO SANDRA MABEL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>73</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DE LA CRUZ BENITES RICHARD ALEXANDER</t>
+          <t>YZQUIERDO CARHUATANTA LEYDY YANELA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>YZQUIERDO CARHUATANTA LEYDY YANELA</t>
+          <t>VALER VEGA PATRICIA GERALDINE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VALER VEGA PATRICIA GERALDINE</t>
+          <t>SANCHEZ CORTEZ LEYLA DIANA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>68</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RODRIGUEZ RUBIO SANDRA MABEL</t>
+          <t>CYNTHIA RODRIGUEZ LECCA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CARRILLO MARTÍNEZ HEIDY NAYELI</t>
+          <t>DE LA CRUZ BENITES RICHARD ALEXANDER</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PONCE VILLANUEVA CARMEN ISABEL</t>
+          <t>RUBIO MARIÑOS GISELA JUDITH</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RUBIO MARIÑOS GISELA JUDITH</t>
+          <t>PONCE VILLANUEVA CARMEN ISABEL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GASLAC GUTIERREZ FRANK JHORDY</t>
+          <t>CARRILLO MARTÍNEZ HEIDY NAYELI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ARENAS ZAVALA ANDYELA PATRICIA ISIDORA</t>
+          <t>GASLAC GUTIERREZ FRANK JHORDY</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PIERINA NAGIELLY SANDOVAL CONTRERAS</t>
+          <t>ARENAS ZAVALA ANDYELA PATRICIA ISIDORA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -577,17 +577,17 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CYNTHIA RODRIGUEZ LECCA</t>
+          <t>PIERINA NAGIELLY SANDOVAL CONTRERAS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>56</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21">

--- a/data/data_monitoreo_huanchaquito.xlsx
+++ b/data/data_monitoreo_huanchaquito.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3">
@@ -457,147 +457,147 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RODRIGUEZ RUBIO SANDRA MABEL</t>
+          <t>YZQUIERDO CARHUATANTA LEYDY YANELA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>YZQUIERDO CARHUATANTA LEYDY YANELA</t>
+          <t>RODRIGUEZ RUBIO SANDRA MABEL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VALER VEGA PATRICIA GERALDINE</t>
+          <t>DE LA CRUZ BENITES RICHARD ALEXANDER</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SANCHEZ CORTEZ LEYLA DIANA</t>
+          <t>VALER VEGA PATRICIA GERALDINE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CYNTHIA RODRIGUEZ LECCA</t>
+          <t>PIERINA NAGIELLY SANDOVAL CONTRERAS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DE LA CRUZ BENITES RICHARD ALEXANDER</t>
+          <t>RUBIO MARIÑOS GISELA JUDITH</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RUBIO MARIÑOS GISELA JUDITH</t>
+          <t>CYNTHIA RODRIGUEZ LECCA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PONCE VILLANUEVA CARMEN ISABEL</t>
+          <t>SANCHEZ CORTEZ LEYLA DIANA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CARRILLO MARTÍNEZ HEIDY NAYELI</t>
+          <t>PONCE VILLANUEVA CARMEN ISABEL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GASLAC GUTIERREZ FRANK JHORDY</t>
+          <t>CARRILLO MARTÍNEZ HEIDY NAYELI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ARENAS ZAVALA ANDYELA PATRICIA ISIDORA</t>
+          <t>GASLAC GUTIERREZ FRANK JHORDY</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEGURA ASTO YAMILET ANTONELA</t>
+          <t>REYES RODRIGUEZ JEISSON STEVEN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PIERINA NAGIELLY SANDOVAL CONTRERAS</t>
+          <t>ARENAS ZAVALA ANDYELA PATRICIA ISIDORA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>REYES RODRIGUEZ JEISSON STEVEN</t>
+          <t>SEGURA ASTO YAMILET ANTONELA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21">

--- a/data/data_monitoreo_huanchaquito.xlsx
+++ b/data/data_monitoreo_huanchaquito.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7">
@@ -503,41 +503,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PIERINA NAGIELLY SANDOVAL CONTRERAS</t>
+          <t>SANCHEZ CORTEZ LEYLA DIANA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RUBIO MARIÑOS GISELA JUDITH</t>
+          <t>CYNTHIA RODRIGUEZ LECCA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CYNTHIA RODRIGUEZ LECCA</t>
+          <t>RUBIO MARIÑOS GISELA JUDITH</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SANCHEZ CORTEZ LEYLA DIANA</t>
+          <t>PIERINA NAGIELLY SANDOVAL CONTRERAS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -567,33 +567,33 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>REYES RODRIGUEZ JEISSON STEVEN</t>
+          <t>SEGURA ASTO YAMILET ANTONELA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARENAS ZAVALA ANDYELA PATRICIA ISIDORA</t>
+          <t>REYES RODRIGUEZ JEISSON STEVEN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEGURA ASTO YAMILET ANTONELA</t>
+          <t>ARENAS ZAVALA ANDYELA PATRICIA ISIDORA</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -603,31 +603,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RODRIGUEZ VASQUEZ WALTER</t>
+          <t>GUZMAN ZAVALETA CECILIA MARISOL</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GUZMAN ZAVALETA CECILIA MARISOL</t>
+          <t>LEON VERA MELISSA FIORELLA</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LEON VERA MELISSA FIORELLA</t>
+          <t>RODRIGUEZ VASQUEZ WALTER</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21">

--- a/data/data_monitoreo_huanchaquito.xlsx
+++ b/data/data_monitoreo_huanchaquito.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>156</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3">
@@ -457,27 +457,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>148</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>YZQUIERDO CARHUATANTA LEYDY YANELA</t>
+          <t>RODRIGUEZ RUBIO SANDRA MABEL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RODRIGUEZ RUBIO SANDRA MABEL</t>
+          <t>YZQUIERDO CARHUATANTA LEYDY YANELA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
@@ -487,127 +487,127 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VALER VEGA PATRICIA GERALDINE</t>
+          <t>CYNTHIA RODRIGUEZ LECCA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SANCHEZ CORTEZ LEYLA DIANA</t>
+          <t>RODRIGUEZ VASQUEZ WALTER</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CYNTHIA RODRIGUEZ LECCA</t>
+          <t>PIERINA NAGIELLY SANDOVAL CONTRERAS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RUBIO MARIÑOS GISELA JUDITH</t>
+          <t>ARENAS ZAVALA ANDYELA PATRICIA ISIDORA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PIERINA NAGIELLY SANDOVAL CONTRERAS</t>
+          <t>VALER VEGA PATRICIA GERALDINE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PONCE VILLANUEVA CARMEN ISABEL</t>
+          <t>RUBIO MARIÑOS GISELA JUDITH</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CARRILLO MARTÍNEZ HEIDY NAYELI</t>
+          <t>REYES RODRIGUEZ JEISSON STEVEN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GASLAC GUTIERREZ FRANK JHORDY</t>
+          <t>PONCE VILLANUEVA CARMEN ISABEL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEGURA ASTO YAMILET ANTONELA</t>
+          <t>SANCHEZ CORTEZ LEYLA DIANA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>REYES RODRIGUEZ JEISSON STEVEN</t>
+          <t>CARRILLO MARTÍNEZ HEIDY NAYELI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>95</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ARENAS ZAVALA ANDYELA PATRICIA ISIDORA</t>
+          <t>SEGURA ASTO YAMILET ANTONELA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GUZMAN ZAVALETA CECILIA MARISOL</t>
+          <t>GASLAC GUTIERREZ FRANK JHORDY</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>79</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19">
@@ -617,17 +617,17 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RODRIGUEZ VASQUEZ WALTER</t>
+          <t>GUZMAN ZAVALETA CECILIA MARISOL</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21">

--- a/data/data_monitoreo_huanchaquito.xlsx
+++ b/data/data_monitoreo_huanchaquito.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>188</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3">
@@ -457,27 +457,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RODRIGUEZ RUBIO SANDRA MABEL</t>
+          <t>YZQUIERDO CARHUATANTA LEYDY YANELA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>YZQUIERDO CARHUATANTA LEYDY YANELA</t>
+          <t>RODRIGUEZ RUBIO SANDRA MABEL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9">
@@ -517,17 +517,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARENAS ZAVALA ANDYELA PATRICIA ISIDORA</t>
+          <t>SANCHEZ CORTEZ LEYLA DIANA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
@@ -537,47 +537,47 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RUBIO MARIÑOS GISELA JUDITH</t>
+          <t>ARENAS ZAVALA ANDYELA PATRICIA ISIDORA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>REYES RODRIGUEZ JEISSON STEVEN</t>
+          <t>LEON VERA MELISSA FIORELLA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PONCE VILLANUEVA CARMEN ISABEL</t>
+          <t>RUBIO MARIÑOS GISELA JUDITH</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SANCHEZ CORTEZ LEYLA DIANA</t>
+          <t>REYES RODRIGUEZ JEISSON STEVEN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16">
@@ -587,37 +587,37 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEGURA ASTO YAMILET ANTONELA</t>
+          <t>PONCE VILLANUEVA CARMEN ISABEL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GASLAC GUTIERREZ FRANK JHORDY</t>
+          <t>SEGURA ASTO YAMILET ANTONELA</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LEON VERA MELISSA FIORELLA</t>
+          <t>GASLAC GUTIERREZ FRANK JHORDY</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21">
